--- a/temp/MRI_Result.xlsx
+++ b/temp/MRI_Result.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F130"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -438,116 +438,121 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>LT_hours</v>
+        <v>球管更换记录</v>
       </c>
       <c r="C2" t="str">
         <v>-</v>
       </c>
       <c r="D2" t="str">
-        <v>LT_hours</v>
+        <v>球管更换记录</v>
       </c>
       <c r="E2" t="str">
-        <v>-</v>
+        <v>中文说明：该关键字在日志中通常表示球管的更换记录，可能包括具体的更换时间、操作人员等信息。</v>
       </c>
       <c r="F2" t="str">
         <v>-</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>HT_hours</v>
+        <v>球管序列号</v>
       </c>
       <c r="C3" t="str">
-        <v>-</v>
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
       </c>
       <c r="D3" t="str">
-        <v>Hours</v>
-      </c>
-      <c r="E3" t="str">
-        <v>该关键字在日志中通常表示小时数，用于衡量时间长度或时间间隔。</v>
+        <v>SerialNumber</v>
+      </c>
+      <c r="E3" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_ASSEMBLY
+&lt;Serial&gt;957092582&lt;/Serial&gt;</v>
       </c>
       <c r="F3" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>2026-06-27 07:37:33.392 DEBUG tvsched   Maximum number of polled sockets increased from 0 to 1</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>HT_hours</v>
+        <v>球管序列号</v>
       </c>
       <c r="C4" t="str">
-        <v>-</v>
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
       </c>
       <c r="D4" t="str">
-        <v>Hour</v>
-      </c>
-      <c r="E4" t="str">
-        <v>该关键字在日志中通常表示小时数，用于衡量时间长度或时间间隔。</v>
+        <v>TubeSerialNumber</v>
+      </c>
+      <c r="E4" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_ASSEMBLY
+&lt;Serial&gt;957092582&lt;/Serial&gt;</v>
       </c>
       <c r="F4" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>2026-06-27 07:37:33.392 DEBUG tvsched   Maximum number of polled sockets increased from 0 to 1</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>HT_hours</v>
+        <v>球管序列号</v>
       </c>
       <c r="C5" t="str">
-        <v>-</v>
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
       </c>
       <c r="D5" t="str">
-        <v>HT_hours</v>
-      </c>
-      <c r="E5" t="str">
-        <v>该关键字在日志中通常表示小时数，用于衡量时间长度或时间间隔。</v>
+        <v>XRayTubeSerial</v>
+      </c>
+      <c r="E5" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_ASSEMBLY
+&lt;Serial&gt;957092582&lt;/Serial&gt;</v>
       </c>
       <c r="F5" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>2017-08-25 13:14:25.7092 Debug Environment - TubeDir:  D:\Tube (ConfigFile)</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Targ_ctrl</v>
+        <v>球管序列号</v>
       </c>
       <c r="C6" t="str">
-        <v>-</v>
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
       </c>
       <c r="D6" t="str">
-        <v>Targ_ctrl</v>
-      </c>
-      <c r="E6" t="str">
-        <v>该关键字在日志中可能表示目标控制或目标管理相关的信息，但具体含义需根据日志内容确定。</v>
+        <v>XRaySerial</v>
+      </c>
+      <c r="E6" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_ASSEMBLY
+&lt;Serial&gt;957092582&lt;/Serial&gt;</v>
       </c>
       <c r="F6" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>...                              | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Coll_ctrl</v>
+        <v>球管序列号</v>
       </c>
       <c r="C7" t="str">
         <v>-</v>
       </c>
       <c r="D7" t="str">
-        <v>Coll_ctrl</v>
-      </c>
-      <c r="E7" t="str">
-        <v>该关键字在日志中通常表示集合控制或管理操作。</v>
+        <v>球管序列号</v>
+      </c>
+      <c r="E7" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_ASSEMBLY
+&lt;Serial&gt;957092582&lt;/Serial&gt;</v>
       </c>
       <c r="F7" t="str">
         <v>-</v>
@@ -558,19 +563,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Coll_ctrl</v>
+        <v>球管型号</v>
       </c>
       <c r="C8" t="str">
-        <v>-</v>
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131403_backup_Tube.log</v>
       </c>
       <c r="D8" t="str">
-        <v>CollectionControl</v>
+        <v>Tube Model</v>
       </c>
       <c r="E8" t="str">
-        <v>该关键字在日志中通常表示集合控制或管理操作。</v>
+        <v>TUBE_TLC_Tube_Type = "MCT_172"</v>
       </c>
       <c r="F8" t="str">
-        <v>-</v>
+        <v>2017-08-25 13:14:03.5098 Debug Environment - TubeDir:  D:\Tube (ConfigFile)</v>
       </c>
     </row>
     <row r="9">
@@ -578,16 +583,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Coll_ctrl</v>
+        <v>球管型号</v>
       </c>
       <c r="C9" t="str">
         <v>-</v>
       </c>
       <c r="D9" t="str">
-        <v>ControlCollection</v>
+        <v>Anode Model</v>
       </c>
       <c r="E9" t="str">
-        <v>该关键字在日志中通常表示集合控制或管理操作。</v>
+        <v>TUBE_TLC_Tube_Type = "MCT_172"</v>
       </c>
       <c r="F9" t="str">
         <v>-</v>
@@ -598,96 +603,100 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Sctr_ctrl</v>
+        <v>球管型号</v>
       </c>
       <c r="C10" t="str">
         <v>-</v>
       </c>
       <c r="D10" t="str">
-        <v>status_control</v>
+        <v>球管型号</v>
       </c>
       <c r="E10" t="str">
-        <v>该关键字在日志中通常表示状态控制或控制状态。</v>
+        <v>TUBE_TLC_Tube_Type = "MCT_172"</v>
       </c>
       <c r="F10" t="str">
         <v>-</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" xml:space="preserve">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Sctr_ctrl</v>
+        <v>球管盒序列号</v>
       </c>
       <c r="C11" t="str">
-        <v>-</v>
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
       </c>
       <c r="D11" t="str">
-        <v>ctrl_status</v>
-      </c>
-      <c r="E11" t="str">
-        <v>该关键字在日志中通常表示状态控制或控制状态。</v>
+        <v>TubeBoxSerialNumber</v>
+      </c>
+      <c r="E11" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_COLLIMATOR
+&lt;Serial&gt;11331&lt;/Serial&gt;</v>
       </c>
       <c r="F11" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>2026-06-27 07:37:33.392 DEBUG tvsched   Maximum number of polled sockets increased from 0 to 1</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Sctr_ctrl</v>
+        <v>球管盒序列号</v>
       </c>
       <c r="C12" t="str">
-        <v>-</v>
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
       </c>
       <c r="D12" t="str">
-        <v>Sctr_ctrl</v>
-      </c>
-      <c r="E12" t="str">
-        <v>该关键字在日志中通常表示状态控制或控制状态。</v>
+        <v>Tube Box Serial Number</v>
+      </c>
+      <c r="E12" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_COLLIMATOR
+&lt;Serial&gt;11331&lt;/Serial&gt;</v>
       </c>
       <c r="F12" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>2026-06-27 07:37:33.392 DEBUG tvsched   Maximum number of polled sockets increased from 0 to 1</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Register_3_part</v>
+        <v>球管盒序列号</v>
       </c>
       <c r="C13" t="str">
-        <v>-</v>
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131403_backup_Tube.log</v>
       </c>
       <c r="D13" t="str">
-        <v>Register_3_part</v>
-      </c>
-      <c r="E13" t="str">
-        <v>-</v>
+        <v>Tube Box SN</v>
+      </c>
+      <c r="E13" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_COLLIMATOR
+&lt;Serial&gt;11331&lt;/Serial&gt;</v>
       </c>
       <c r="F13" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>2017-08-25 13:14:03.5098 Debug Environment - TubeDir:  D:\Tube (ConfigFile)</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Wedge_in</v>
+        <v>球管盒序列号</v>
       </c>
       <c r="C14" t="str">
         <v>-</v>
       </c>
       <c r="D14" t="str">
-        <v>Wedge_in</v>
-      </c>
-      <c r="E14" t="str">
-        <v>-</v>
+        <v>球管盒序列号</v>
+      </c>
+      <c r="E14" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_COLLIMATOR
+&lt;Serial&gt;11331&lt;/Serial&gt;</v>
       </c>
       <c r="F14" t="str">
         <v>-</v>
@@ -698,16 +707,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Gantry</v>
+        <v>球管盒型号</v>
       </c>
       <c r="C15" t="str">
         <v>-</v>
       </c>
       <c r="D15" t="str">
-        <v>Gantry</v>
+        <v>Model</v>
       </c>
       <c r="E15" t="str">
-        <v>该关键字在日志中通常表示一个特定的设备或系统，用于记录与该设备或系统相关的操作和状态信息</v>
+        <v>TUBE_TLC_Tube_Housing_Type = "DURA_688_MC"</v>
       </c>
       <c r="F15" t="str">
         <v>-</v>
@@ -718,19 +727,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>D.Rot.</v>
+        <v>球管盒型号</v>
       </c>
       <c r="C16" t="str">
-        <v>-</v>
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
       </c>
       <c r="D16" t="str">
-        <v>D.Rot.</v>
+        <v>Version</v>
       </c>
       <c r="E16" t="str">
-        <v>-</v>
+        <v>TUBE_TLC_Tube_Housing_Type = "DURA_688_MC"</v>
       </c>
       <c r="F16" t="str">
-        <v>-</v>
+        <v>2026-06-27 07:39:01.525 INFO  tvsched     Version:                1.0.1</v>
       </c>
     </row>
     <row r="17">
@@ -738,19 +747,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>X1</v>
+        <v>球管盒型号</v>
       </c>
       <c r="C17" t="str">
-        <v>-</v>
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131403_backup_Tube.log</v>
       </c>
       <c r="D17" t="str">
-        <v>Error</v>
+        <v>Tube_Holder_Model</v>
       </c>
       <c r="E17" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>TUBE_TLC_Tube_Housing_Type = "DURA_688_MC"</v>
       </c>
       <c r="F17" t="str">
-        <v>-</v>
+        <v>2017-08-25 13:14:03.5098 Debug Environment - TubeDir:  D:\Tube (ConfigFile)</v>
       </c>
     </row>
     <row r="18">
@@ -758,16 +767,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>X1</v>
+        <v>球管盒型号</v>
       </c>
       <c r="C18" t="str">
         <v>-</v>
       </c>
       <c r="D18" t="str">
-        <v>Fault</v>
+        <v>球管盒型号</v>
       </c>
       <c r="E18" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>TUBE_TLC_Tube_Housing_Type = "DURA_688_MC"</v>
       </c>
       <c r="F18" t="str">
         <v>-</v>
@@ -778,19 +787,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>X1</v>
+        <v>安装时间</v>
       </c>
       <c r="C19" t="str">
-        <v>-</v>
+        <v>F:\Somaris\Install\log\ChkPart.log</v>
       </c>
       <c r="D19" t="str">
-        <v>Exception</v>
+        <v>install</v>
       </c>
       <c r="E19" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>中文说明：该关键字在日志中通常表示系统安装或配置的时间。</v>
       </c>
       <c r="F19" t="str">
-        <v>-</v>
+        <v>call diskpart /s C:\Somaris\Install\log\Diskinfo.txt</v>
       </c>
     </row>
     <row r="20">
@@ -798,19 +807,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>X1</v>
+        <v>安装时间</v>
       </c>
       <c r="C20" t="str">
-        <v>-</v>
+        <v>F:\Somaris\Install\log\Codiag.log</v>
       </c>
       <c r="D20" t="str">
-        <v>Problem</v>
+        <v>installation</v>
       </c>
       <c r="E20" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>中文说明：该关键字在日志中通常表示系统安装或配置的时间。</v>
       </c>
       <c r="F20" t="str">
-        <v>-</v>
+        <v>CODIAG_Install_Silent.bat: Set Installation source directory to C:\InstDir\Codiag</v>
       </c>
     </row>
     <row r="21">
@@ -818,19 +827,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>X1</v>
+        <v>安装时间</v>
       </c>
       <c r="C21" t="str">
-        <v>-</v>
+        <v>F:\Somaris\log\SOM_Install.log</v>
       </c>
       <c r="D21" t="str">
-        <v>X1</v>
+        <v>setup</v>
       </c>
       <c r="E21" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>中文说明：该关键字在日志中通常表示系统安装或配置的时间。</v>
       </c>
       <c r="F21" t="str">
-        <v>-</v>
+        <v>Starting C:\InstDir\SOMARIS\Setup\syngoInstaller.exe /GROUPS=P68A Customer /LOGFILE...</v>
       </c>
     </row>
     <row r="22">
@@ -838,19 +847,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>X2</v>
+        <v>安装时间</v>
       </c>
       <c r="C22" t="str">
-        <v>-</v>
+        <v>F:\Somaris\config\service\timezones\ReadMe.txt</v>
       </c>
       <c r="D22" t="str">
-        <v>X2</v>
+        <v>setup_time</v>
       </c>
       <c r="E22" t="str">
-        <v>该关键字在日志中通常表示系统或设备的配置或状态。</v>
+        <v>中文说明：该关键字在日志中通常表示系统安装或配置的时间。</v>
       </c>
       <c r="F22" t="str">
-        <v>-</v>
+        <v>Following Locations do not have the Daylight Savings Time feature available as an option.</v>
       </c>
     </row>
     <row r="23">
@@ -858,16 +867,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>X2</v>
+        <v>安装时间</v>
       </c>
       <c r="C23" t="str">
         <v>-</v>
       </c>
       <c r="D23" t="str">
-        <v>Config</v>
+        <v>安装时间</v>
       </c>
       <c r="E23" t="str">
-        <v>该关键字在日志中通常表示系统或设备的配置或状态。</v>
+        <v>中文说明：该关键字在日志中通常表示系统安装或配置的时间。</v>
       </c>
       <c r="F23" t="str">
         <v>-</v>
@@ -878,19 +887,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>X2</v>
+        <v>最后扫描时间</v>
       </c>
       <c r="C24" t="str">
-        <v>-</v>
+        <v>F:\Somaris\config\ScanGuideCtImageTextConfig.txt</v>
       </c>
       <c r="D24" t="str">
-        <v>Setting</v>
+        <v>LastScanTime</v>
       </c>
       <c r="E24" t="str">
-        <v>该关键字在日志中通常表示系统或设备的配置或状态。</v>
+        <v>该关键字在日志中通常表示设备上一次完成扫描的时间点。</v>
       </c>
       <c r="F24" t="str">
-        <v>-</v>
+        <v>BEGIN_LINE "Acquisition Time"</v>
       </c>
     </row>
     <row r="25">
@@ -898,19 +907,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Y1</v>
+        <v>最后扫描时间</v>
       </c>
       <c r="C25" t="str">
-        <v>-</v>
+        <v>F:\Somaris\config\ScanGuideCtImageTextConfig.txt</v>
       </c>
       <c r="D25" t="str">
-        <v>Y1</v>
+        <v>Last_Scan_Time</v>
       </c>
       <c r="E25" t="str">
-        <v>由于缺乏具体信息，无法提供关键字的中文说明</v>
+        <v>该关键字在日志中通常表示设备上一次完成扫描的时间点。</v>
       </c>
       <c r="F25" t="str">
-        <v>-</v>
+        <v>BEGIN_LINE "Acquisition Time"</v>
       </c>
     </row>
     <row r="26">
@@ -918,19 +927,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Y2</v>
+        <v>最后扫描时间</v>
       </c>
       <c r="C26" t="str">
-        <v>-</v>
+        <v>F:\Somaris\config\ScanGuideCtImageTextConfig.txt</v>
       </c>
       <c r="D26" t="str">
-        <v>Y2</v>
+        <v>Latest_Scan_Time</v>
       </c>
       <c r="E26" t="str">
-        <v>该关键字在日志中通常表示与系统性能相关的特定指标。</v>
+        <v>该关键字在日志中通常表示设备上一次完成扫描的时间点。</v>
       </c>
       <c r="F26" t="str">
-        <v>-</v>
+        <v>BEGIN_LINE "Acquisition Time"</v>
       </c>
     </row>
     <row r="27">
@@ -938,16 +947,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>Y2</v>
+        <v>最后扫描时间</v>
       </c>
       <c r="C27" t="str">
         <v>-</v>
       </c>
       <c r="D27" t="str">
-        <v>Performance</v>
+        <v>最后扫描时间</v>
       </c>
       <c r="E27" t="str">
-        <v>该关键字在日志中通常表示与系统性能相关的特定指标。</v>
+        <v>该关键字在日志中通常表示设备上一次完成扫描的时间点。</v>
       </c>
       <c r="F27" t="str">
         <v>-</v>
@@ -958,31 +967,2071 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Y2</v>
+        <v>累计检查病人数</v>
       </c>
       <c r="C28" t="str">
-        <v>-</v>
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
       </c>
       <c r="D28" t="str">
-        <v>Metrics</v>
+        <v>PatientCount</v>
       </c>
       <c r="E28" t="str">
-        <v>该关键字在日志中通常表示与系统性能相关的特定指标。</v>
+        <v>该关键字在日志中通常表示累计检查病人数，可能记录在系统日志或操作日志中。</v>
       </c>
       <c r="F28" t="str">
+        <v>...Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>累计检查病人数</v>
+      </c>
+      <c r="C29" t="str">
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
+      </c>
+      <c r="D29" t="str">
+        <v>NumberOfPatients</v>
+      </c>
+      <c r="E29" t="str">
+        <v>该关键字在日志中通常表示累计检查病人数，可能记录在系统日志或操作日志中。</v>
+      </c>
+      <c r="F29" t="str">
+        <v>2026-06-27 07:37:33.392 DEBUG tvpeer    State of peer 0x8d3838 (ADMIN_SERVER) changed from 1 (WAIT...</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>累计检查病人数</v>
+      </c>
+      <c r="C30" t="str">
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
+      </c>
+      <c r="D30" t="str">
+        <v>NumberOfChecks</v>
+      </c>
+      <c r="E30" t="str">
+        <v>该关键字在日志中通常表示累计检查病人数，可能记录在系统日志或操作日志中。</v>
+      </c>
+      <c r="F30" t="str">
+        <v>2026-06-27 07:37:33.392 DEBUG tvpeer    State of peer 0x8d3838 (ADMIN_SERVER) changed from 1 (WAIT...</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>累计检查病人数</v>
+      </c>
+      <c r="C31" t="str">
+        <v>F:\Somaris\log\ServiceBootHook.1.log</v>
+      </c>
+      <c r="D31" t="str">
+        <v>CheckCount</v>
+      </c>
+      <c r="E31" t="str">
+        <v>该关键字在日志中通常表示累计检查病人数，可能记录在系统日志或操作日志中。</v>
+      </c>
+      <c r="F31" t="str">
+        <v>check TransferMgr</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>累计检查病人数</v>
+      </c>
+      <c r="C32" t="str">
+        <v>-</v>
+      </c>
+      <c r="D32" t="str">
+        <v>累计检查病人数</v>
+      </c>
+      <c r="E32" t="str">
+        <v>该关键字在日志中通常表示累计检查病人数，可能记录在系统日志或操作日志中。</v>
+      </c>
+      <c r="F32" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>累计电流时长</v>
+      </c>
+      <c r="C33" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D33" t="str">
+        <v>CumulativeCurrentDuration</v>
+      </c>
+      <c r="E33" t="str">
+        <v>&lt;CurrentTotalTubeCharge&gt;3807533.21&lt;/CurrentTotalTubeCharge&gt;</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2017-08-25 13:14:25.7267 Info Main - Current Hostname  : ct120959</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>累计电流时长</v>
+      </c>
+      <c r="C34" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D34" t="str">
+        <v>CurrentDuration</v>
+      </c>
+      <c r="E34" t="str">
+        <v>&lt;CurrentTotalTubeCharge&gt;3807533.21&lt;/CurrentTotalTubeCharge&gt;</v>
+      </c>
+      <c r="F34" t="str">
+        <v>2017-08-25 13:14:25.7267 Info Main - Current Hostname  : ct120959</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>累计电流时长</v>
+      </c>
+      <c r="C35" t="str">
+        <v>-</v>
+      </c>
+      <c r="D35" t="str">
+        <v>CumulativeTime</v>
+      </c>
+      <c r="E35" t="str">
+        <v>&lt;CurrentTotalTubeCharge&gt;3807533.21&lt;/CurrentTotalTubeCharge&gt;</v>
+      </c>
+      <c r="F35" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>累计电流时长</v>
+      </c>
+      <c r="C36" t="str">
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
+      </c>
+      <c r="D36" t="str">
+        <v>RunningTime</v>
+      </c>
+      <c r="E36" t="str">
+        <v>&lt;CurrentTotalTubeCharge&gt;3807533.21&lt;/CurrentTotalTubeCharge&gt;</v>
+      </c>
+      <c r="F36" t="str">
+        <v>...27 07:37:33.704 INFO  main      Child process was running for 2 days, 23 hours, 39 minutes, 45 seconds; die...</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>累计电流时长</v>
+      </c>
+      <c r="C37" t="str">
+        <v>-</v>
+      </c>
+      <c r="D37" t="str">
+        <v>累计电流时长</v>
+      </c>
+      <c r="E37" t="str">
+        <v>&lt;CurrentTotalTubeCharge&gt;3807533.21&lt;/CurrentTotalTubeCharge&gt;</v>
+      </c>
+      <c r="F37" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>累计曝光次数</v>
+      </c>
+      <c r="C38" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D38" t="str">
+        <v>cumulativeExposureCount</v>
+      </c>
+      <c r="E38" t="str">
+        <v>该关键字在日志中通常表示在一定时间段内累积的曝光次数。</v>
+      </c>
+      <c r="F38" t="str">
+        <v>...Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>累计曝光次数</v>
+      </c>
+      <c r="C39" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D39" t="str">
+        <v>totalExposureCount</v>
+      </c>
+      <c r="E39" t="str">
+        <v>该关键字在日志中通常表示在一定时间段内累积的曝光次数。</v>
+      </c>
+      <c r="F39" t="str">
+        <v>2017-08-25 13:14:26.2712 Info Summary -                      Total  =&gt;  OK   /  Warning   /   Error</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>累计曝光次数</v>
+      </c>
+      <c r="C40" t="str">
+        <v>-</v>
+      </c>
+      <c r="D40" t="str">
+        <v>累计曝光次数</v>
+      </c>
+      <c r="E40" t="str">
+        <v>该关键字在日志中通常表示在一定时间段内累积的曝光次数。</v>
+      </c>
+      <c r="F40" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>累计能耗</v>
+      </c>
+      <c r="C41" t="str">
+        <v>F:\InstDir\Codiag\FTS_DV\APPLICATION\DVCONNECT\DEFAULTCONFIG.DEU.XML</v>
+      </c>
+      <c r="D41" t="str">
+        <v>EnergyUsage</v>
+      </c>
+      <c r="E41" t="str">
+        <v>该关键字在日志中通常表示累计能耗，可能包含具体能耗数据或相关计算值。</v>
+      </c>
+      <c r="F41" t="str">
+        <v>&lt;value id="0x0065" text="Energy Saving"/&gt;</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>累计能耗</v>
+      </c>
+      <c r="C42" t="str">
+        <v>F:\CMPNENTS\Workaround_Add_Printer\TCPMON.INI</v>
+      </c>
+      <c r="D42" t="str">
+        <v>PowerConsumption</v>
+      </c>
+      <c r="E42" t="str">
+        <v>该关键字在日志中通常表示累计能耗，可能包含具体能耗数据或相关计算值。</v>
+      </c>
+      <c r="F42" t="str">
+        <v>"Oce Power Print Controller Master*"         = OCE_84x5_92xx</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>累计能耗</v>
+      </c>
+      <c r="C43" t="str">
+        <v>F:\InstDir\Codiag\FTS_DV\APPLICATION\DVCONNECT\DEFAULTCONFIG.DEU.XML</v>
+      </c>
+      <c r="D43" t="str">
+        <v>CumulativeEnergy</v>
+      </c>
+      <c r="E43" t="str">
+        <v>该关键字在日志中通常表示累计能耗，可能包含具体能耗数据或相关计算值。</v>
+      </c>
+      <c r="F43" t="str">
+        <v>&lt;value id="0x0065" text="Energy Saving"/&gt;</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>累计能耗</v>
+      </c>
+      <c r="C44" t="str">
+        <v>-</v>
+      </c>
+      <c r="D44" t="str">
+        <v>累计能耗</v>
+      </c>
+      <c r="E44" t="str">
+        <v>该关键字在日志中通常表示累计能耗，可能包含具体能耗数据或相关计算值。</v>
+      </c>
+      <c r="F44" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>累计扫描时长</v>
+      </c>
+      <c r="C45" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D45" t="str">
+        <v>CumulativeScanDuration</v>
+      </c>
+      <c r="E45" t="str">
+        <v>&lt;/Scan&gt;&lt;Scan time</v>
+      </c>
+      <c r="F45" t="str">
+        <v>...   | Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>累计扫描时长</v>
+      </c>
+      <c r="C46" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D46" t="str">
+        <v>TotalScanTime</v>
+      </c>
+      <c r="E46" t="str">
+        <v>&lt;/Scan&gt;&lt;Scan time</v>
+      </c>
+      <c r="F46" t="str">
+        <v>2017-08-25 13:14:26.2712 Info Summary -                      Total  =&gt;  OK   /  Warning   /   Error</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>累计扫描时长</v>
+      </c>
+      <c r="C47" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D47" t="str">
+        <v>TotalScanDuration</v>
+      </c>
+      <c r="E47" t="str">
+        <v>&lt;/Scan&gt;&lt;Scan time</v>
+      </c>
+      <c r="F47" t="str">
+        <v>2017-08-25 13:14:26.2712 Info Summary -                      Total  =&gt;  OK   /  Warning   /   Error</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>累计扫描时长</v>
+      </c>
+      <c r="C48" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D48" t="str">
+        <v>ScanTime</v>
+      </c>
+      <c r="E48" t="str">
+        <v>&lt;/Scan&gt;&lt;Scan time</v>
+      </c>
+      <c r="F48" t="str">
+        <v>...   | Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>累计扫描时长</v>
+      </c>
+      <c r="C49" t="str">
+        <v>-</v>
+      </c>
+      <c r="D49" t="str">
+        <v>累计扫描时长</v>
+      </c>
+      <c r="E49" t="str">
+        <v>&lt;/Scan&gt;&lt;Scan time</v>
+      </c>
+      <c r="F49" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>扫描部位</v>
+      </c>
+      <c r="C50" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131413_backup_ServQua_Error.log</v>
+      </c>
+      <c r="D50" t="str">
+        <v>ScanSite</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F50" t="str">
+        <v>...Registry key HKLM\SOFTWARE\Siemens\SOMARIS\Config\Site\servicetune\QUA_CTDI_BASELINE_GB not found</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>扫描部位</v>
+      </c>
+      <c r="C51" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D51" t="str">
+        <v>ScanArea</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F51" t="str">
+        <v>...   | Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>扫描部位</v>
+      </c>
+      <c r="C52" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131413_backup_ServQua_Error.log</v>
+      </c>
+      <c r="D52" t="str">
+        <v>AnatomicSite</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F52" t="str">
+        <v>...Registry key HKLM\SOFTWARE\Siemens\SOMARIS\Config\Site\servicetune\QUA_CTDI_BASELINE_GB not found</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>扫描部位</v>
+      </c>
+      <c r="C53" t="str">
+        <v>-</v>
+      </c>
+      <c r="D53" t="str">
+        <v>BodyPartExamined</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F53" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>扫描部位</v>
+      </c>
+      <c r="C54" t="str">
+        <v>-</v>
+      </c>
+      <c r="D54" t="str">
+        <v>扫描部位</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F54" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>检查部位</v>
+      </c>
+      <c r="C55" t="str">
+        <v>-</v>
+      </c>
+      <c r="D55" t="str">
+        <v>ExamArea</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F55" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>检查部位</v>
+      </c>
+      <c r="C56" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131413_backup_ServQua_Error.log</v>
+      </c>
+      <c r="D56" t="str">
+        <v>ScanSite</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F56" t="str">
+        <v>...Registry key HKLM\SOFTWARE\Siemens\SOMARIS\Config\Site\servicetune\QUA_CTDI_BASELINE_GB not found</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>检查部位</v>
+      </c>
+      <c r="C57" t="str">
+        <v>-</v>
+      </c>
+      <c r="D57" t="str">
+        <v>BodyPart</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F57" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>检查部位</v>
+      </c>
+      <c r="C58" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131413_backup_ServQua_Error.log</v>
+      </c>
+      <c r="D58" t="str">
+        <v>ImagingSite</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F58" t="str">
+        <v>...Registry key HKLM\SOFTWARE\Siemens\SOMARIS\Config\Site\servicetune\QUA_CTDI_BASELINE_GB not found</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>检查部位</v>
+      </c>
+      <c r="C59" t="str">
+        <v>-</v>
+      </c>
+      <c r="D59" t="str">
+        <v>检查部位</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Body part examined</v>
+      </c>
+      <c r="F59" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>检查开始时间</v>
+      </c>
+      <c r="C60" t="str">
+        <v>F:\Somaris\config\service\timezones\ReadMe.txt</v>
+      </c>
+      <c r="D60" t="str">
+        <v>startTime</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Recon begin</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Following Locations do not have the Daylight Savings Time feature available as an option.</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>检查开始时间</v>
+      </c>
+      <c r="C61" t="str">
+        <v>F:\Somaris\config\service\timezones\ReadMe.txt</v>
+      </c>
+      <c r="D61" t="str">
+        <v>start_time</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Recon begin</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Following Locations do not have the Daylight Savings Time feature available as an option.</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>检查开始时间</v>
+      </c>
+      <c r="C62" t="str">
+        <v>F:\Somaris\config\service\timezones\ReadMe.txt</v>
+      </c>
+      <c r="D62" t="str">
+        <v>begin_time</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Recon begin</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Following Locations do not have the Daylight Savings Time feature available as an option.</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>检查开始时间</v>
+      </c>
+      <c r="C63" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D63" t="str">
+        <v>timestamp</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Recon begin</v>
+      </c>
+      <c r="F63" t="str">
+        <v>2017-08-25 13:14:25.7417 Info Framework - Write timestamp '2017-08-25T13:14:25+08:00' for 'LastBackup_Start...</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>检查开始时间</v>
+      </c>
+      <c r="C64" t="str">
+        <v>-</v>
+      </c>
+      <c r="D64" t="str">
+        <v>检查开始时间</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Recon begin</v>
+      </c>
+      <c r="F64" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>检查结束时间</v>
+      </c>
+      <c r="C65" t="str">
+        <v>F:\Somaris\config\service\timezones\ReadMe.txt</v>
+      </c>
+      <c r="D65" t="str">
+        <v>End Time</v>
+      </c>
+      <c r="E65" t="str">
+        <v>ReconDone</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Following Locations do not have the Daylight Savings Time feature available as an option.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>检查结束时间</v>
+      </c>
+      <c r="C66" t="str">
+        <v>F:\Somaris\config\service\timezones\ReadMe.txt</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Completion Time</v>
+      </c>
+      <c r="E66" t="str">
+        <v>ReconDone</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Following Locations do not have the Daylight Savings Time feature available as an option.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>检查结束时间</v>
+      </c>
+      <c r="C67" t="str">
+        <v>F:\Somaris\config\service\timezones\ReadMe.txt</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Finish Time</v>
+      </c>
+      <c r="E67" t="str">
+        <v>ReconDone</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Following Locations do not have the Daylight Savings Time feature available as an option.</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>检查结束时间</v>
+      </c>
+      <c r="C68" t="str">
+        <v>-</v>
+      </c>
+      <c r="D68" t="str">
+        <v>检查结束时间</v>
+      </c>
+      <c r="E68" t="str">
+        <v>ReconDone</v>
+      </c>
+      <c r="F68" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>检查编号</v>
+      </c>
+      <c r="C69" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D69" t="str">
+        <v>CheckID</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Accession number</v>
+      </c>
+      <c r="F69" t="str">
+        <v>2017-08-25 13:14:25.6967 Info Init - ID: 0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>检查编号</v>
+      </c>
+      <c r="C70" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D70" t="str">
+        <v>ExamID</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Accession number</v>
+      </c>
+      <c r="F70" t="str">
+        <v>2017-08-25 13:14:25.6967 Info Init - ID: 0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>检查编号</v>
+      </c>
+      <c r="C71" t="str">
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
+      </c>
+      <c r="D71" t="str">
+        <v>ExamNumber</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Accession number</v>
+      </c>
+      <c r="F71" t="str">
+        <v>2026-06-27 07:37:33.392 DEBUG tvsched   Maximum number of polled sockets increased from 0 to 1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>检查编号</v>
+      </c>
+      <c r="C72" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D72" t="str">
+        <v>SessionID</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Accession number</v>
+      </c>
+      <c r="F72" t="str">
+        <v>2017-08-25 13:14:25.6967 Info Init - ID: 0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>检查编号</v>
+      </c>
+      <c r="C73" t="str">
+        <v>-</v>
+      </c>
+      <c r="D73" t="str">
+        <v>检查编号</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Accession number</v>
+      </c>
+      <c r="F73" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>扫描方法</v>
+      </c>
+      <c r="C74" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D74" t="str">
+        <v>ScanMethod</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Kind</v>
+      </c>
+      <c r="F74" t="str">
+        <v>...   | Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>扫描方法</v>
+      </c>
+      <c r="C75" t="str">
+        <v>-</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Method</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Kind</v>
+      </c>
+      <c r="F75" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>扫描方法</v>
+      </c>
+      <c r="C76" t="str">
+        <v>-</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Procedure</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Kind</v>
+      </c>
+      <c r="F76" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>扫描方法</v>
+      </c>
+      <c r="C77" t="str">
+        <v>-</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Technique</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Kind</v>
+      </c>
+      <c r="F77" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>扫描方法</v>
+      </c>
+      <c r="C78" t="str">
+        <v>-</v>
+      </c>
+      <c r="D78" t="str">
+        <v>扫描方法</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Kind</v>
+      </c>
+      <c r="F78" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>扫描序列</v>
+      </c>
+      <c r="C79" t="str">
+        <v>F:\Somaris\config\ScanGuideCtImageTextConfig.txt</v>
+      </c>
+      <c r="D79" t="str">
+        <v>ScanSequence</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Recon job type</v>
+      </c>
+      <c r="F79" t="str">
+        <v>BEGIN_LINE "Scan type&amp;number"</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>扫描序列</v>
+      </c>
+      <c r="C80" t="str">
+        <v>F:\Somaris\config\ScanGuideCtImageTextConfig.txt</v>
+      </c>
+      <c r="D80" t="str">
+        <v>ScanSeq</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Recon job type</v>
+      </c>
+      <c r="F80" t="str">
+        <v>BEGIN_LINE "Scan type&amp;number"</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>扫描序列</v>
+      </c>
+      <c r="C81" t="str">
+        <v>F:\Somaris\config\ScanGuideCtImageTextConfig.txt</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Scan_Seq</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Recon job type</v>
+      </c>
+      <c r="F81" t="str">
+        <v>BEGIN_LINE "Scan type&amp;number"</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>扫描序列</v>
+      </c>
+      <c r="C82" t="str">
+        <v>-</v>
+      </c>
+      <c r="D82" t="str">
+        <v>扫描序列</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Recon job type</v>
+      </c>
+      <c r="F82" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>阳极温度</v>
+      </c>
+      <c r="C83" t="str">
+        <v>-</v>
+      </c>
+      <c r="D83" t="str">
+        <v>AnodeTemperature</v>
+      </c>
+      <c r="E83" t="str">
+        <v>该关键字在日志中通常表示CT设备X射线管的温度。</v>
+      </c>
+      <c r="F83" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>阳极温度</v>
+      </c>
+      <c r="C84" t="str">
+        <v>F:\Somaris\log\bareserviceXML.log</v>
+      </c>
+      <c r="D84" t="str">
+        <v>XRayAnodeTemp</v>
+      </c>
+      <c r="E84" t="str">
+        <v>该关键字在日志中通常表示CT设备X射线管的温度。</v>
+      </c>
+      <c r="F84" t="str">
+        <v>executing C:\Somaris\bin\siteident.exe 100 C:\Temp\bareService\siteident\customer.xml</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>阳极温度</v>
+      </c>
+      <c r="C85" t="str">
+        <v>-</v>
+      </c>
+      <c r="D85" t="str">
+        <v>AnodeHeat</v>
+      </c>
+      <c r="E85" t="str">
+        <v>该关键字在日志中通常表示CT设备X射线管的温度。</v>
+      </c>
+      <c r="F85" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>阳极温度</v>
+      </c>
+      <c r="C86" t="str">
+        <v>-</v>
+      </c>
+      <c r="D86" t="str">
+        <v>阳极温度</v>
+      </c>
+      <c r="E86" t="str">
+        <v>该关键字在日志中通常表示CT设备X射线管的温度。</v>
+      </c>
+      <c r="F86" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>磁盘大小/使用率</v>
+      </c>
+      <c r="C87" t="str">
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
+      </c>
+      <c r="D87" t="str">
+        <v>DiskSize</v>
+      </c>
+      <c r="E87" t="str">
+        <v>该关键字在日志中通常表示磁盘的大小或使用率，可能包括具体的数值或百分比。</v>
+      </c>
+      <c r="F87" t="str">
+        <v>2026-06-27 07:39:01.525 INFO  tvsched     Log File Size:          5000000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>磁盘大小/使用率</v>
+      </c>
+      <c r="C88" t="str">
+        <v>F:\Somaris\log\IptCheckForDiskSpace.log</v>
+      </c>
+      <c r="D88" t="str">
+        <v>DiskUsage</v>
+      </c>
+      <c r="E88" t="str">
+        <v>该关键字在日志中通常表示磁盘的大小或使用率，可能包括具体的数值或百分比。</v>
+      </c>
+      <c r="F88" t="str">
+        <v>checking disk space in  C:\Temp 500m CSA_IP E80000CA</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
+        <v>磁盘大小/使用率</v>
+      </c>
+      <c r="C89" t="str">
+        <v>F:\Somaris\log\IptCheckForDiskSpace.log</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Space</v>
+      </c>
+      <c r="E89" t="str">
+        <v>该关键字在日志中通常表示磁盘的大小或使用率，可能包括具体的数值或百分比。</v>
+      </c>
+      <c r="F89" t="str">
+        <v>checking disk space in  C:\Temp 500m CSA_IP E80000CA</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
+        <v>磁盘大小/使用率</v>
+      </c>
+      <c r="C90" t="str">
+        <v>-</v>
+      </c>
+      <c r="D90" t="str">
+        <v>磁盘大小/使用率</v>
+      </c>
+      <c r="E90" t="str">
+        <v>该关键字在日志中通常表示磁盘的大小或使用率，可能包括具体的数值或百分比。</v>
+      </c>
+      <c r="F90" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
+        <v>开机统计</v>
+      </c>
+      <c r="C91" t="str">
+        <v>F:\Somaris\config\SysStatFilter_Startup.txt</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Startup</v>
+      </c>
+      <c r="E91" t="str">
+        <v>开机统计在日志中通常表示系统启动或初始化的过程。</v>
+      </c>
+      <c r="F91" t="str">
+        <v>CSA_OSC 267 startup</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
+        <v>开机统计</v>
+      </c>
+      <c r="C92" t="str">
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Init</v>
+      </c>
+      <c r="E92" t="str">
+        <v>开机统计在日志中通常表示系统启动或初始化的过程。</v>
+      </c>
+      <c r="F92" t="str">
+        <v>2026-06-28 07:41:56.998 DEBUG tvcmdevnt init(): operation=TERMINATE_REQ, maxRunTime=2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
+        <v>开机统计</v>
+      </c>
+      <c r="C93" t="str">
+        <v>-</v>
+      </c>
+      <c r="D93" t="str">
+        <v>开机统计</v>
+      </c>
+      <c r="E93" t="str">
+        <v>开机统计在日志中通常表示系统启动或初始化的过程。</v>
+      </c>
+      <c r="F93" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
+        <v>关机统计</v>
+      </c>
+      <c r="C94" t="str">
+        <v>F:\Somaris\log\Backup_Dynamic_Shutdown.1.log</v>
+      </c>
+      <c r="D94" t="str">
+        <v>ShutDown</v>
+      </c>
+      <c r="E94" t="str">
+        <v>中文说明：该关键字在日志中通常表示设备的关机操作。</v>
+      </c>
+      <c r="F94" t="str">
+        <v>### I. CHECK IF IT IS A SYSTEM SHUTDOWN /-RESTART OR AN APPLICATION RESTART</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="str">
+        <v>关机统计</v>
+      </c>
+      <c r="C95" t="str">
+        <v>-</v>
+      </c>
+      <c r="D95" t="str">
+        <v>PowerOff</v>
+      </c>
+      <c r="E95" t="str">
+        <v>中文说明：该关键字在日志中通常表示设备的关机操作。</v>
+      </c>
+      <c r="F95" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="str">
+        <v>关机统计</v>
+      </c>
+      <c r="C96" t="str">
+        <v>-</v>
+      </c>
+      <c r="D96" t="str">
+        <v>关机统计</v>
+      </c>
+      <c r="E96" t="str">
+        <v>中文说明：该关键字在日志中通常表示设备的关机操作。</v>
+      </c>
+      <c r="F96" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="str">
+        <v>校准统计</v>
+      </c>
+      <c r="C97" t="str">
+        <v>-</v>
+      </c>
+      <c r="D97" t="str">
+        <v>CalibrationStatistics</v>
+      </c>
+      <c r="E97" t="str">
+        <v>统计文件数量Calibration_2026-08-26_08-02-49.htm</v>
+      </c>
+      <c r="F97" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="str">
+        <v>校准统计</v>
+      </c>
+      <c r="C98" t="str">
+        <v>-</v>
+      </c>
+      <c r="D98" t="str">
+        <v>CalibStat</v>
+      </c>
+      <c r="E98" t="str">
+        <v>统计文件数量Calibration_2026-08-26_08-02-49.htm</v>
+      </c>
+      <c r="F98" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="str">
+        <v>校准统计</v>
+      </c>
+      <c r="C99" t="str">
+        <v>-</v>
+      </c>
+      <c r="D99" t="str">
+        <v>AccurateStat</v>
+      </c>
+      <c r="E99" t="str">
+        <v>统计文件数量Calibration_2026-08-26_08-02-49.htm</v>
+      </c>
+      <c r="F99" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="str">
+        <v>校准统计</v>
+      </c>
+      <c r="C100" t="str">
+        <v>-</v>
+      </c>
+      <c r="D100" t="str">
+        <v>校准统计</v>
+      </c>
+      <c r="E100" t="str">
+        <v>统计文件数量Calibration_2026-08-26_08-02-49.htm</v>
+      </c>
+      <c r="F100" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>预热统计</v>
+      </c>
+      <c r="C101" t="str">
+        <v>-</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Preheat</v>
+      </c>
+      <c r="E101" t="str">
+        <v>该关键字在日志中通常表示设备启动或重启后的预热阶段。</v>
+      </c>
+      <c r="F101" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>预热统计</v>
+      </c>
+      <c r="C102" t="str">
+        <v>-</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Warmup</v>
+      </c>
+      <c r="E102" t="str">
+        <v>该关键字在日志中通常表示设备启动或重启后的预热阶段。</v>
+      </c>
+      <c r="F102" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>预热统计</v>
+      </c>
+      <c r="C103" t="str">
+        <v>F:\Somaris\config\SysStatFilter_Startup.txt</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Startup</v>
+      </c>
+      <c r="E103" t="str">
+        <v>该关键字在日志中通常表示设备启动或重启后的预热阶段。</v>
+      </c>
+      <c r="F103" t="str">
+        <v>CSA_OSC 267 startup</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>预热统计</v>
+      </c>
+      <c r="C104" t="str">
+        <v>-</v>
+      </c>
+      <c r="D104" t="str">
+        <v>预热统计</v>
+      </c>
+      <c r="E104" t="str">
+        <v>该关键字在日志中通常表示设备启动或重启后的预热阶段。</v>
+      </c>
+      <c r="F104" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>错误日志</v>
+      </c>
+      <c r="C105" t="str">
+        <v>F:\PnPDrv\M720_R920\TEXTMODE\MEGARAID_LSI_LOGIC_9_00_01\LSIMPTWIN7_2008R2.TXT</v>
+      </c>
+      <c r="D105" t="str">
+        <v>error</v>
+      </c>
+      <c r="E105" t="str">
+        <v>该关键字在日志中通常表示系统或应用程序的异常状态或错误信息。</v>
+      </c>
+      <c r="F105" t="str">
+        <v>The LSI_SCSI.SYS, LSI_FC.SYS and LSI_SAS.SYS driver will log error messages to</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>错误日志</v>
+      </c>
+      <c r="C106" t="str">
+        <v>F:\PnPDrv\M720_R920\TEXTMODE\MEGARAID_LSI_LOGIC_9_00_01\LSIMPTWIN7_2008R2.TXT</v>
+      </c>
+      <c r="D106" t="str">
+        <v>log</v>
+      </c>
+      <c r="E106" t="str">
+        <v>该关键字在日志中通常表示系统或应用程序的异常状态或错误信息。</v>
+      </c>
+      <c r="F106" t="str">
+        <v>the system error log. For these errors, the system errorlog EventID will be 11,</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>错误日志</v>
+      </c>
+      <c r="C107" t="str">
+        <v>-</v>
+      </c>
+      <c r="D107" t="str">
+        <v>错误日志</v>
+      </c>
+      <c r="E107" t="str">
+        <v>该关键字在日志中通常表示系统或应用程序的异常状态或错误信息。</v>
+      </c>
+      <c r="F107" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>球管打火数</v>
+      </c>
+      <c r="C108" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D108" t="str">
+        <v>SparkCount</v>
+      </c>
+      <c r="E108" t="str">
+        <v>该关键字在日志中通常表示球管在特定时间段内发生的打火次数。</v>
+      </c>
+      <c r="F108" t="str">
+        <v>...Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>球管打火数</v>
+      </c>
+      <c r="C109" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D109" t="str">
+        <v>IgnitionCount</v>
+      </c>
+      <c r="E109" t="str">
+        <v>该关键字在日志中通常表示球管在特定时间段内发生的打火次数。</v>
+      </c>
+      <c r="F109" t="str">
+        <v>...Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>球管打火数</v>
+      </c>
+      <c r="C110" t="str">
+        <v>-</v>
+      </c>
+      <c r="D110" t="str">
+        <v>球管打火数</v>
+      </c>
+      <c r="E110" t="str">
+        <v>该关键字在日志中通常表示球管在特定时间段内发生的打火次数。</v>
+      </c>
+      <c r="F110" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>系统时间/主机时间</v>
+      </c>
+      <c r="C111" t="str">
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
+      </c>
+      <c r="D111" t="str">
+        <v>SystemTime HostTime</v>
+      </c>
+      <c r="E111" t="str">
+        <v>该关键字在日志中通常表示系统或主机的当前时间戳。</v>
+      </c>
+      <c r="F111" t="str">
+        <v>2026-06-27 07:39:01.525 INFO  tvsched   System information:</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>系统时间/主机时间</v>
+      </c>
+      <c r="C112" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Timestamp</v>
+      </c>
+      <c r="E112" t="str">
+        <v>该关键字在日志中通常表示系统或主机的当前时间戳。</v>
+      </c>
+      <c r="F112" t="str">
+        <v>2017-08-25 13:14:25.7417 Info Framework - Write timestamp '2017-08-25T13:14:25+08:00' for 'LastBackup_Start...</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>系统时间/主机时间</v>
+      </c>
+      <c r="C113" t="str">
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
+      </c>
+      <c r="D113" t="str">
+        <v>DateTime</v>
+      </c>
+      <c r="E113" t="str">
+        <v>该关键字在日志中通常表示系统或主机的当前时间戳。</v>
+      </c>
+      <c r="F113" t="str">
+        <v>2026-06-27 07:39:01.525 INFO  tvsched     Creation date:          2015-04-28 17:24:27</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>系统时间/主机时间</v>
+      </c>
+      <c r="C114" t="str">
+        <v>-</v>
+      </c>
+      <c r="D114" t="str">
+        <v>系统时间/主机时间</v>
+      </c>
+      <c r="E114" t="str">
+        <v>该关键字在日志中通常表示系统或主机的当前时间戳。</v>
+      </c>
+      <c r="F114" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>累计扫描次数</v>
+      </c>
+      <c r="C115" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D115" t="str">
+        <v>CumulativeScanCount</v>
+      </c>
+      <c r="E115" t="str">
+        <v>Scan count</v>
+      </c>
+      <c r="F115" t="str">
+        <v>...   | Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>累计扫描次数</v>
+      </c>
+      <c r="C116" t="str">
+        <v>F:\Somaris\log\BaReXML\2017-08-25_131425_backup_EventLog.log</v>
+      </c>
+      <c r="D116" t="str">
+        <v>TotalScans</v>
+      </c>
+      <c r="E116" t="str">
+        <v>Scan count</v>
+      </c>
+      <c r="F116" t="str">
+        <v>2017-08-25 13:14:26.2712 Info Summary -                      Total  =&gt;  OK   /  Warning   /   Error</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>累计扫描次数</v>
+      </c>
+      <c r="C117" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D117" t="str">
+        <v>ScanCount</v>
+      </c>
+      <c r="E117" t="str">
+        <v>Scan count</v>
+      </c>
+      <c r="F117" t="str">
+        <v>...   | Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>累计扫描次数</v>
+      </c>
+      <c r="C118" t="str">
+        <v>-</v>
+      </c>
+      <c r="D118" t="str">
+        <v>累计扫描次数</v>
+      </c>
+      <c r="E118" t="str">
+        <v>Scan count</v>
+      </c>
+      <c r="F118" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>扫描次数</v>
+      </c>
+      <c r="C119" t="str">
+        <v>F:\Somaris\log\TubeEventLog2026-08-04_07-56-36-226.log</v>
+      </c>
+      <c r="D119" t="str">
+        <v>ScanCount</v>
+      </c>
+      <c r="E119" t="str">
+        <v>Scan count</v>
+      </c>
+      <c r="F119" t="str">
+        <v>...   | Type | Value                               | Scan count | Tube serial number | System serial number</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>扫描次数</v>
+      </c>
+      <c r="C120" t="str">
+        <v>F:\Somaris\CrspTeamViewer\Teamviewer-Gateway\log\tvgwservice.log</v>
+      </c>
+      <c r="D120" t="str">
+        <v>NumberOfScans</v>
+      </c>
+      <c r="E120" t="str">
+        <v>Scan count</v>
+      </c>
+      <c r="F120" t="str">
+        <v>2026-06-27 07:37:33.392 DEBUG tvpeer    State of peer 0x8d3838 (ADMIN_SERVER) changed from 1 (WAIT...</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>扫描次数</v>
+      </c>
+      <c r="C121" t="str">
+        <v>-</v>
+      </c>
+      <c r="D121" t="str">
+        <v>扫描次数</v>
+      </c>
+      <c r="E121" t="str">
+        <v>Scan count</v>
+      </c>
+      <c r="F121" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>扫描协议</v>
+      </c>
+      <c r="C122" t="str">
+        <v>F:\Somaris\config\mri\MrProtocol\N3ProtMappingTable.txt</v>
+      </c>
+      <c r="D122" t="str">
+        <v>protocol</v>
+      </c>
+      <c r="E122" t="str">
+        <v>JobName</v>
+      </c>
+      <c r="F122" t="str">
+        <v># Available Special handlings for Protocol data:</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>扫描协议</v>
+      </c>
+      <c r="C123" t="str">
+        <v>F:\Somaris\config\mri\MrProtocol\N3ProtMappingTable.txt</v>
+      </c>
+      <c r="D123" t="str">
+        <v>scan_protocol</v>
+      </c>
+      <c r="E123" t="str">
+        <v>JobName</v>
+      </c>
+      <c r="F123" t="str">
+        <v># Available Special handlings for Protocol data:</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>扫描协议</v>
+      </c>
+      <c r="C124" t="str">
+        <v>-</v>
+      </c>
+      <c r="D124" t="str">
+        <v>setting</v>
+      </c>
+      <c r="E124" t="str">
+        <v>JobName</v>
+      </c>
+      <c r="F124" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>扫描协议</v>
+      </c>
+      <c r="C125" t="str">
+        <v>F:\Somaris\config\ScanGuideCtImageTextConfig.txt</v>
+      </c>
+      <c r="D125" t="str">
+        <v>configuration</v>
+      </c>
+      <c r="E125" t="str">
+        <v>JobName</v>
+      </c>
+      <c r="F125" t="str">
+        <v>// ImageText configuration created at: Tue Dec 15 10:30:49 2009</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>扫描协议</v>
+      </c>
+      <c r="C126" t="str">
+        <v>-</v>
+      </c>
+      <c r="D126" t="str">
+        <v>扫描协议</v>
+      </c>
+      <c r="E126" t="str">
+        <v>JobName</v>
+      </c>
+      <c r="F126" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>探测器机架入风口温度</v>
+      </c>
+      <c r="C127" t="str">
+        <v>F:\Somaris\config\SysStatFilter_Temperature.txt</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Temperature</v>
+      </c>
+      <c r="E127" t="str">
+        <v>该关键字在日志中通常表示探测器机架入风口的温度测量值。</v>
+      </c>
+      <c r="F127" t="str">
+        <v>CT_ITF 1 (?:Temperature|Voltage)</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>探测器机架入风口温度</v>
+      </c>
+      <c r="C128" t="str">
+        <v>F:\Somaris\log\bareserviceXML.log</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Temp</v>
+      </c>
+      <c r="E128" t="str">
+        <v>该关键字在日志中通常表示探测器机架入风口的温度测量值。</v>
+      </c>
+      <c r="F128" t="str">
+        <v>executing C:\Somaris\bin\siteident.exe 100 C:\Temp\bareService\siteident\customer.xml</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>探测器机架入风口温度</v>
+      </c>
+      <c r="C129" t="str">
+        <v>-</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Heat</v>
+      </c>
+      <c r="E129" t="str">
+        <v>该关键字在日志中通常表示探测器机架入风口的温度测量值。</v>
+      </c>
+      <c r="F129" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>探测器机架入风口温度</v>
+      </c>
+      <c r="C130" t="str">
+        <v>-</v>
+      </c>
+      <c r="D130" t="str">
+        <v>探测器机架入风口温度</v>
+      </c>
+      <c r="E130" t="str">
+        <v>该关键字在日志中通常表示探测器机架入风口的温度测量值。</v>
+      </c>
+      <c r="F130" t="str">
         <v>-</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F130"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F52"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -1014,10 +3063,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LT_hours</v>
+        <v>球管更换记录</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>MriSiteData, SysUtil</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -1026,18 +3075,18 @@
         <v/>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>中文说明：该关键字在日志中通常表示球管的更换记录，可能包括具体的更换时间、操作人员等信息。</v>
       </c>
       <c r="F2" t="str">
         <v>文件未找到或关键字未匹配</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>HT_hours</v>
+        <v>球管序列号</v>
       </c>
       <c r="B3" t="str">
-        <v>SysLog, SysUtil</v>
+        <v>H:\Somaris\log\ctconfig.xml</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -1045,8 +3094,9 @@
       <c r="D3" t="str">
         <v/>
       </c>
-      <c r="E3" t="str">
-        <v>该关键字在日志中通常表示小时数，用于衡量时间长度或时间间隔。</v>
+      <c r="E3" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_ASSEMBLY
+&lt;Serial&gt;957092582&lt;/Serial&gt;</v>
       </c>
       <c r="F3" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1054,10 +3104,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HT_hours</v>
+        <v>球管型号</v>
       </c>
       <c r="B4" t="str">
-        <v>SysLog, SysUtil</v>
+        <v>H:\Somaris\config\m_somaris_tubetlc.spec</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -1066,7 +3116,7 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>该关键字在日志中通常表示小时数，用于衡量时间长度或时间间隔。</v>
+        <v>TUBE_TLC_Tube_Type = "MCT_172"</v>
       </c>
       <c r="F4" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1074,10 +3124,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HT_hours</v>
+        <v>球管型号</v>
       </c>
       <c r="B5" t="str">
-        <v>SysLog, SysUtil</v>
+        <v>H:\Somaris\config\m_somaris_tubetlc.spec</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -1086,18 +3136,18 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>该关键字在日志中通常表示小时数，用于衡量时间长度或时间间隔。</v>
+        <v>TUBE_TLC_Tube_Type = "MCT_172"</v>
       </c>
       <c r="F5" t="str">
         <v>文件未找到或关键字未匹配</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>Targ_ctrl</v>
+        <v>球管盒序列号</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>H:\Somaris\log\ctconfig.xml</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -1105,8 +3155,9 @@
       <c r="D6" t="str">
         <v/>
       </c>
-      <c r="E6" t="str">
-        <v>该关键字在日志中可能表示目标控制或目标管理相关的信息，但具体含义需根据日志内容确定。</v>
+      <c r="E6" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUBE_COLLIMATOR
+&lt;Serial&gt;11331&lt;/Serial&gt;</v>
       </c>
       <c r="F6" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1114,10 +3165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Coll_ctrl</v>
+        <v>球管盒型号</v>
       </c>
       <c r="B7" t="str">
-        <v>SysLog, Config</v>
+        <v>H:\Somaris\config\m_somaris_tubetlc.spec</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -1126,7 +3177,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>该关键字在日志中通常表示集合控制或管理操作。</v>
+        <v>TUBE_TLC_Tube_Housing_Type = "DURA_688_MC"</v>
       </c>
       <c r="F7" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1134,10 +3185,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Coll_ctrl</v>
+        <v>球管盒型号</v>
       </c>
       <c r="B8" t="str">
-        <v>SysLog, Config</v>
+        <v>H:\Somaris\config\m_somaris_tubetlc.spec</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -1146,7 +3197,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>该关键字在日志中通常表示集合控制或管理操作。</v>
+        <v>TUBE_TLC_Tube_Housing_Type = "DURA_688_MC"</v>
       </c>
       <c r="F8" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1154,10 +3205,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Coll_ctrl</v>
+        <v>安装时间</v>
       </c>
       <c r="B9" t="str">
-        <v>SysLog, Config</v>
+        <v>SystemInit</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -1166,7 +3217,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>该关键字在日志中通常表示集合控制或管理操作。</v>
+        <v>中文说明：该关键字在日志中通常表示系统安装或配置的时间。</v>
       </c>
       <c r="F9" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1174,10 +3225,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sctr_ctrl</v>
+        <v>最后扫描时间</v>
       </c>
       <c r="B10" t="str">
-        <v>ControlLogs, StatusLogs</v>
+        <v>MriSiteData, SysUtil</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -1186,7 +3237,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>该关键字在日志中通常表示状态控制或控制状态。</v>
+        <v>该关键字在日志中通常表示设备上一次完成扫描的时间点。</v>
       </c>
       <c r="F10" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1194,10 +3245,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Sctr_ctrl</v>
+        <v>累计检查病人数</v>
       </c>
       <c r="B11" t="str">
-        <v>ControlLogs, StatusLogs</v>
+        <v>SysLog, OperationLog</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -1206,7 +3257,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>该关键字在日志中通常表示状态控制或控制状态。</v>
+        <v>该关键字在日志中通常表示累计检查病人数，可能记录在系统日志或操作日志中。</v>
       </c>
       <c r="F11" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1214,10 +3265,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Sctr_ctrl</v>
+        <v>累计电流时长</v>
       </c>
       <c r="B12" t="str">
-        <v>ControlLogs, StatusLogs</v>
+        <v>H:\Somaris\tube\ScanTimeOverview.xml</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -1226,7 +3277,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>该关键字在日志中通常表示状态控制或控制状态。</v>
+        <v>&lt;CurrentTotalTubeCharge&gt;3807533.21&lt;/CurrentTotalTubeCharge&gt;</v>
       </c>
       <c r="F12" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1234,10 +3285,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Register_3_part</v>
+        <v>累计电流时长</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>H:\Somaris\tube\ScanTimeOverview.xml</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -1246,7 +3297,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>&lt;CurrentTotalTubeCharge&gt;3807533.21&lt;/CurrentTotalTubeCharge&gt;</v>
       </c>
       <c r="F13" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1254,10 +3305,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Wedge_in</v>
+        <v>累计曝光次数</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>CTLog, CTData</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -1266,7 +3317,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>该关键字在日志中通常表示在一定时间段内累积的曝光次数。</v>
       </c>
       <c r="F14" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1274,10 +3325,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Gantry</v>
+        <v>累计能耗</v>
       </c>
       <c r="B15" t="str">
-        <v>GantryLog, GantrySys</v>
+        <v>EnergyUsage</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -1286,7 +3337,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>该关键字在日志中通常表示一个特定的设备或系统，用于记录与该设备或系统相关的操作和状态信息</v>
+        <v>该关键字在日志中通常表示累计能耗，可能包含具体能耗数据或相关计算值。</v>
       </c>
       <c r="F15" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1294,10 +3345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>D.Rot.</v>
+        <v>累计扫描时长</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>H:\Somaris\Tube\ScanTimeOverview.xml</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -1306,7 +3357,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>&lt;/Scan&gt;&lt;Scan time</v>
       </c>
       <c r="F16" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1314,10 +3365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>X1</v>
+        <v>扫描部位</v>
       </c>
       <c r="B17" t="str">
-        <v>ErrorLogs</v>
+        <v>H:\Somaris\log\EventLog\EvtApplication_20260828.txt.gz</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -1326,7 +3377,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>Body part examined</v>
       </c>
       <c r="F17" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1334,10 +3385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>X1</v>
+        <v>扫描部位</v>
       </c>
       <c r="B18" t="str">
-        <v>ErrorLogs</v>
+        <v>H:\Somaris\log\EventLog\EvtApplication_20260828.txt.gz</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -1346,7 +3397,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>Body part examined</v>
       </c>
       <c r="F18" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1354,10 +3405,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>X1</v>
+        <v>检查部位</v>
       </c>
       <c r="B19" t="str">
-        <v>ErrorLogs</v>
+        <v>H:\Somaris\log\EventLog\EvtApplication_20260828.txt.gz</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -1366,7 +3417,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>Body part examined</v>
       </c>
       <c r="F19" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1374,10 +3425,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>X1</v>
+        <v>检查部位</v>
       </c>
       <c r="B20" t="str">
-        <v>ErrorLogs</v>
+        <v>H:\Somaris\log\EventLog\EvtApplication_20260828.txt.gz</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -1386,7 +3437,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>Body part examined</v>
       </c>
       <c r="F20" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1394,10 +3445,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>X1</v>
+        <v>检查部位</v>
       </c>
       <c r="B21" t="str">
-        <v>ErrorLogs</v>
+        <v>H:\Somaris\log\EventLog\EvtApplication_20260828.txt.gz</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -1406,7 +3457,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>该关键字在日志中通常表示系统或程序中的错误或异常情况。</v>
+        <v>Body part examined</v>
       </c>
       <c r="F21" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1414,10 +3465,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>X2</v>
+        <v>检查开始时间</v>
       </c>
       <c r="B22" t="str">
-        <v>SysConfig</v>
+        <v>H:\Somaris\log\EventLog\EvtApplication_20260828.txt.gz</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -1426,7 +3477,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>该关键字在日志中通常表示系统或设备的配置或状态。</v>
+        <v>Recon begin</v>
       </c>
       <c r="F22" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1434,10 +3485,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>X2</v>
+        <v>检查结束时间</v>
       </c>
       <c r="B23" t="str">
-        <v>SysConfig</v>
+        <v>H:\Somaris\log\EventLog\EvtApplication_20260828.txt.gz</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -1446,7 +3497,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>该关键字在日志中通常表示系统或设备的配置或状态。</v>
+        <v>ReconDone</v>
       </c>
       <c r="F23" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1454,10 +3505,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>X2</v>
+        <v>检查编号</v>
       </c>
       <c r="B24" t="str">
-        <v>SysConfig</v>
+        <v>H:\Somaris\log\EventLog\EvtApplication_20260828.txt.gz</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -1466,7 +3517,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>该关键字在日志中通常表示系统或设备的配置或状态。</v>
+        <v>Accession number</v>
       </c>
       <c r="F24" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1474,10 +3525,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Y1</v>
+        <v>扫描方法</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>MedCom/log, Scan, SysUtil</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -1486,7 +3537,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>由于缺乏具体信息，无法提供关键字的中文说明</v>
+        <v>Kind</v>
       </c>
       <c r="F25" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1494,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Y2</v>
+        <v>扫描方法</v>
       </c>
       <c r="B26" t="str">
-        <v>PerformanceLogs</v>
+        <v>MedCom/log, Scan, SysUtil</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -1506,7 +3557,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>该关键字在日志中通常表示与系统性能相关的特定指标。</v>
+        <v>Kind</v>
       </c>
       <c r="F26" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1514,10 +3565,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Y2</v>
+        <v>扫描方法</v>
       </c>
       <c r="B27" t="str">
-        <v>PerformanceLogs</v>
+        <v>MedCom/log, Scan, SysUtil</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -1526,7 +3577,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>该关键字在日志中通常表示与系统性能相关的特定指标。</v>
+        <v>Kind</v>
       </c>
       <c r="F27" t="str">
         <v>文件未找到或关键字未匹配</v>
@@ -1534,10 +3585,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Y2</v>
+        <v>扫描方法</v>
       </c>
       <c r="B28" t="str">
-        <v>PerformanceLogs</v>
+        <v>MedCom/log, Scan, SysUtil</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -1546,22 +3597,502 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>该关键字在日志中通常表示与系统性能相关的特定指标。</v>
+        <v>Kind</v>
       </c>
       <c r="F28" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>扫描序列</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Scan, Sequence, SysUtil</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v>Recon job type</v>
+      </c>
+      <c r="F29" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>阳极温度</v>
+      </c>
+      <c r="B30" t="str">
+        <v>XRay/Temp</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>该关键字在日志中通常表示CT设备X射线管的温度。</v>
+      </c>
+      <c r="F30" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>阳极温度</v>
+      </c>
+      <c r="B31" t="str">
+        <v>XRay/Temp</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v>该关键字在日志中通常表示CT设备X射线管的温度。</v>
+      </c>
+      <c r="F31" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>阳极温度</v>
+      </c>
+      <c r="B32" t="str">
+        <v>XRay/Temp</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v>该关键字在日志中通常表示CT设备X射线管的温度。</v>
+      </c>
+      <c r="F32" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>磁盘大小/使用率</v>
+      </c>
+      <c r="B33" t="str">
+        <v>SysUtil</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v>该关键字在日志中通常表示磁盘的大小或使用率，可能包括具体的数值或百分比。</v>
+      </c>
+      <c r="F33" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>开机统计</v>
+      </c>
+      <c r="B34" t="str">
+        <v>SystemLog</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v>开机统计在日志中通常表示系统启动或初始化的过程。</v>
+      </c>
+      <c r="F34" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>关机统计</v>
+      </c>
+      <c r="B35" t="str">
+        <v>SysUtil</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v>中文说明：该关键字在日志中通常表示设备的关机操作。</v>
+      </c>
+      <c r="F35" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>关机统计</v>
+      </c>
+      <c r="B36" t="str">
+        <v>SysUtil</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v>中文说明：该关键字在日志中通常表示设备的关机操作。</v>
+      </c>
+      <c r="F36" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>校准统计</v>
+      </c>
+      <c r="B37" t="str">
+        <v>H:\Somaris\service\html\report\htmlreport</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v>统计文件数量Calibration_2026-08-26_08-02-49.htm</v>
+      </c>
+      <c r="F37" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>校准统计</v>
+      </c>
+      <c r="B38" t="str">
+        <v>H:\Somaris\service\html\report\htmlreport</v>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v>统计文件数量Calibration_2026-08-26_08-02-49.htm</v>
+      </c>
+      <c r="F38" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>校准统计</v>
+      </c>
+      <c r="B39" t="str">
+        <v>H:\Somaris\service\html\report\htmlreport</v>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v>统计文件数量Calibration_2026-08-26_08-02-49.htm</v>
+      </c>
+      <c r="F39" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>校准统计</v>
+      </c>
+      <c r="B40" t="str">
+        <v>H:\Somaris\service\html\report\htmlreport</v>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v>统计文件数量Calibration_2026-08-26_08-02-49.htm</v>
+      </c>
+      <c r="F40" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>预热统计</v>
+      </c>
+      <c r="B41" t="str">
+        <v>SysUtil, MriSiteData</v>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v>该关键字在日志中通常表示设备启动或重启后的预热阶段。</v>
+      </c>
+      <c r="F41" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>预热统计</v>
+      </c>
+      <c r="B42" t="str">
+        <v>SysUtil, MriSiteData</v>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v>该关键字在日志中通常表示设备启动或重启后的预热阶段。</v>
+      </c>
+      <c r="F42" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>预热统计</v>
+      </c>
+      <c r="B43" t="str">
+        <v>SysUtil, MriSiteData</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v>该关键字在日志中通常表示设备启动或重启后的预热阶段。</v>
+      </c>
+      <c r="F43" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>错误日志</v>
+      </c>
+      <c r="B44" t="str">
+        <v>ErrorLog, Log/error</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v>该关键字在日志中通常表示系统或应用程序的异常状态或错误信息。</v>
+      </c>
+      <c r="F44" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>球管打火数</v>
+      </c>
+      <c r="B45" t="str">
+        <v>SysUtil, MriSiteData</v>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v>该关键字在日志中通常表示球管在特定时间段内发生的打火次数。</v>
+      </c>
+      <c r="F45" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>系统时间/主机时间</v>
+      </c>
+      <c r="B46" t="str">
+        <v>SysLog, TimeService</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v>该关键字在日志中通常表示系统或主机的当前时间戳。</v>
+      </c>
+      <c r="F46" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>累计扫描次数</v>
+      </c>
+      <c r="B47" t="str">
+        <v>H:\Somaris\log\TubeEventLog2026-08-29_07-56-27-883.log</v>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v>Scan count</v>
+      </c>
+      <c r="F47" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>扫描次数</v>
+      </c>
+      <c r="B48" t="str">
+        <v>H:\Somaris\log\TubeEventLog2026-08-29_07-56-27-883.log</v>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v>Scan count</v>
+      </c>
+      <c r="F48" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>扫描协议</v>
+      </c>
+      <c r="B49" t="str">
+        <v>CTScanConfig, ProtocolSettings, ScanSettings</v>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v>JobName</v>
+      </c>
+      <c r="F49" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>扫描协议</v>
+      </c>
+      <c r="B50" t="str">
+        <v>CTScanConfig, ProtocolSettings, ScanSettings</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v>JobName</v>
+      </c>
+      <c r="F50" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>探测器机架入风口温度</v>
+      </c>
+      <c r="B51" t="str">
+        <v>H:\Somaris\log\GantryTemp.txt</v>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v>该关键字在日志中通常表示探测器机架入风口的温度测量值。</v>
+      </c>
+      <c r="F51" t="str">
+        <v>文件未找到或关键字未匹配</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>探测器机架入风口温度</v>
+      </c>
+      <c r="B52" t="str">
+        <v>H:\Somaris\log\GantryTemp.txt</v>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v>该关键字在日志中通常表示探测器机架入风口的温度测量值。</v>
+      </c>
+      <c r="F52" t="str">
         <v>文件未找到或关键字未匹配</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F52"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -1580,7 +4111,7 @@
         <v>扫描时间</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-01T09:20:37.467Z</v>
+        <v>2026-09-02T02:00:38.934Z</v>
       </c>
     </row>
     <row r="3">
@@ -1588,7 +4119,7 @@
         <v>目标磁盘</v>
       </c>
       <c r="B3" t="str">
-        <v>D:\</v>
+        <v>F:\</v>
       </c>
     </row>
     <row r="4">
@@ -1596,7 +4127,7 @@
         <v>扫描文件总数</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="5">
@@ -1604,7 +4135,7 @@
         <v>成功采集数</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -1612,7 +4143,7 @@
         <v>失败/未找到数</v>
       </c>
       <c r="B6">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -1620,7 +4151,7 @@
         <v>总指标数</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -1628,7 +4159,7 @@
         <v>耗时(秒)</v>
       </c>
       <c r="B8" t="str">
-        <v>14.32</v>
+        <v>327.47</v>
       </c>
     </row>
     <row r="9">
@@ -1636,7 +4167,7 @@
         <v>模板规则数</v>
       </c>
       <c r="B9">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +4196,7 @@
         <v>未匹配</v>
       </c>
       <c r="B13" t="str">
-        <v>27 个指标</v>
+        <v>129 个指标</v>
       </c>
     </row>
     <row r="14">
@@ -1681,9 +4212,17 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&lt;60%（低可信）</v>
+      </c>
+      <c r="B16" t="str">
+        <v>78 个指标</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B16"/>
   </ignoredErrors>
 </worksheet>
 </file>